--- a/题库/Python理论练习题1.xlsx
+++ b/题库/Python理论练习题1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="143">
   <si>
     <t>题号</t>
   </si>
@@ -438,21 +438,56 @@
     <t>程序填空</t>
   </si>
   <si>
-    <t>程序填空：遍历字典的键和值，使用【1】和【2】方法。</t>
-  </si>
-  <si>
-    <t>【1】keys()（遍历字典所有键）；【2】values()（遍历字典所有值）；【补充】items()（遍历字典键值对，返回(key, value)元组）</t>
+    <r>
+      <t>点击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>答题</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进行答题</t>
+    </r>
+  </si>
+  <si>
+    <t>【1】s.append(x)；
+【2】s[i],s[j] = s[j],s[i]；</t>
   </si>
   <si>
     <t>Prog00011.py</t>
   </si>
   <si>
-    <t>程序填空：判断素数相关函数，三处填空。</t>
-  </si>
-  <si>
-    <t>填空1：if n &lt;= 1: return False（小于等于1的数不是素数）；
-填空2：for i in range(2, int(n**0.5)+1)（循环到根号n即可，提高效率）；
-填空3：if n % i == 0: return False（能被整除则不是素数）</t>
+    <t>【1】：int
+【2】：and</t>
   </si>
   <si>
     <t>Prog00012.py</t>
@@ -461,12 +496,9 @@
     <t>程序改错</t>
   </si>
   <si>
-    <t>程序改错：修改求完全数程序中的三处错误。</t>
-  </si>
-  <si>
-    <t>错误1：循环起始值应为2（原代码可能从1开始，1是所有数的因子，会导致结果错误）；
-错误2：累加因子时应使用i而非n（原代码可能误写为n，导致累加错误）；
-错误3：判断完全数的条件应为sum == n（原代码可能是sum = n赋值语句，而非判断语句）</t>
+    <t>【1】if x.isdigit() and int(x)&gt;0:
+【2】while t&gt;0:
+【3】t=x</t>
   </si>
   <si>
     <t>Prog00013.py</t>
@@ -482,7 +514,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,6 +534,12 @@
       <sz val="11.25"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -648,6 +686,12 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -990,137 +1034,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1138,6 +1182,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2635,14 +2682,14 @@
       <c r="B46" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I46" s="6">
@@ -2659,26 +2706,26 @@
       <c r="B47" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>138</v>
+      <c r="C47" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I47" s="6">
+        <v>10</v>
+      </c>
+      <c r="J47" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="I47" s="6">
-        <v>10</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1" spans="1:10">
       <c r="A48" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2695,23 +2742,23 @@
         <v>43</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="7" t="s">
-        <v>143</v>
+      <c r="H49" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="I49" s="6">
         <v>10</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
